--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-37.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.3%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.4%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.2%</t>
+          <t>422.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-6.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.5%</t>
+          <t>-578.9%</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.2%</t>
+          <t>-50.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>113.6%</t>
+          <t>114.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.4%</t>
+          <t>-320.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-79.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>131.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>120.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>136.2%</t>
+          <t>133.3%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87945506965308</v>
+        <v>-3.927622147495868</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.017803087830866</v>
+        <v>1.998536256693751</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.213626672334268</v>
+        <v>1.16545959449148</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.298117543406407</v>
+        <v>4.269217296700734</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920610189221301</v>
+        <v>-3.968777267064089</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.003221670187714</v>
+        <v>1.983954839050599</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.172471552766047</v>
+        <v>1.124304474923259</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.275305101849611</v>
+        <v>4.246404855143938</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852561626529771</v>
+        <v>-3.900728704372559</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.043292121142208</v>
+        <v>2.024025290005093</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.240520115457577</v>
+        <v>1.192353037614789</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.328985265342411</v>
+        <v>4.300085018636739</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084162019699273</v>
+        <v>-4.13232909754206</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.970854634048002</v>
+        <v>1.951587802910887</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.240520115457577</v>
+        <v>1.192353037614789</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.349187935516005</v>
+        <v>4.320287688810333</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134213565228492</v>
+        <v>-4.18238064307128</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.934440251903196</v>
+        <v>1.915173420766081</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.240520115457577</v>
+        <v>1.192353037614789</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.332794171582887</v>
+        <v>4.303893924877214</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309320397804937</v>
+        <v>-4.357487475647725</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.824649432466085</v>
+        <v>1.80538260132897</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.240520115457577</v>
+        <v>1.192353037614789</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.293046085176353</v>
+        <v>4.264145838470681</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113220244374414</v>
+        <v>-4.161387322217202</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.910112112835234</v>
+        <v>1.890845281698119</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.4366202688881</v>
+        <v>1.388453191045312</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.417728796231607</v>
+        <v>4.388828549525935</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96019485226113</v>
+        <v>-4.008361930103918</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.070493269253452</v>
+        <v>2.051226438116337</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.589645661001384</v>
+        <v>1.541478583158596</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.608715031072482</v>
+        <v>4.57981478436681</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.9885021661344</v>
+        <v>-4.036669243977189</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.246636568612437</v>
+        <v>2.227369737475321</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.589645661001384</v>
+        <v>1.541478583158596</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.796181255980775</v>
+        <v>4.767281009275102</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155095391247922</v>
+        <v>-4.203262469090711</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.14940222992111</v>
+        <v>2.130135398783995</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.423052435887861</v>
+        <v>1.374885358045073</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.665628272266744</v>
+        <v>4.636728025561071</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132059597886356</v>
+        <v>-4.180226675729145</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.162292949927454</v>
+        <v>2.143026118790339</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.423052435887861</v>
+        <v>1.374885358045073</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.669304674928462</v>
+        <v>4.640404428222789</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.10281361743066</v>
+        <v>-4.150980695273448</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.171609397233228</v>
+        <v>2.152342566096113</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.423052435887861</v>
+        <v>1.374885358045073</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.666922730051957</v>
+        <v>4.638022483346284</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.209739165308511</v>
+        <v>-4.257906243151299</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.126132417239723</v>
+        <v>2.106865586102608</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.31612688801001</v>
+        <v>1.267959810167222</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.600060640482882</v>
+        <v>4.571160393777209</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.35475772381576</v>
+        <v>-4.402924801658548</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.069553795980058</v>
+        <v>2.050286964842943</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.171108329502762</v>
+        <v>1.122941251659973</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.514478307521767</v>
+        <v>4.485578060816094</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473099489600477</v>
+        <v>-4.521266567443265</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.122148328923924</v>
+        <v>2.102881497786809</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.181794368065652</v>
+        <v>1.133627290222864</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.620821169917254</v>
+        <v>4.591920923211581</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524509911921185</v>
+        <v>-4.572676989763973</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.099369857121579</v>
+        <v>2.080103025984465</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.181794368065652</v>
+        <v>1.133627290222864</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.618606867043193</v>
+        <v>4.58970662033752</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.603929363128937</v>
+        <v>-4.652096440971725</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.067505204712768</v>
+        <v>2.048238373575653</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.181794368065652</v>
+        <v>1.133627290222864</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.618509995117482</v>
+        <v>4.589609748411809</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699392361046154</v>
+        <v>-4.747559438888943</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.029313899103924</v>
+        <v>2.010047067966809</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.181794368065652</v>
+        <v>1.133627290222864</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.618503888675525</v>
+        <v>4.589603641969852</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635016450195439</v>
+        <v>-4.683183528038228</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.053160660006821</v>
+        <v>2.033893828869705</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.246170278916367</v>
+        <v>1.198003201073579</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.655225831748565</v>
+        <v>4.626325585042892</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690385612327633</v>
+        <v>-4.738552690170422</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.036746812901669</v>
+        <v>2.017479981764555</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.246170278916367</v>
+        <v>1.198003201073579</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.660959649496291</v>
+        <v>4.632059402790619</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.708604079325242</v>
+        <v>-4.75677115716803</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.028997789445559</v>
+        <v>2.009730958308444</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.221063841660525</v>
+        <v>1.172896763817737</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.645434150485719</v>
+        <v>4.616533903780046</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.620397245177664</v>
+        <v>-4.668564323020452</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.084154915954909</v>
+        <v>2.064888084817794</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.221063841660525</v>
+        <v>1.172896763817737</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.665308543336037</v>
+        <v>4.636408296630364</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.514362249972354</v>
+        <v>-4.562529327815143</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.11026961456176</v>
+        <v>2.091002783424645</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.221063841660525</v>
+        <v>1.172896763817737</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.649009243860765</v>
+        <v>4.620108997155092</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.331150586839259</v>
+        <v>-4.379317664682048</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.185985229279044</v>
+        <v>2.166718398141929</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.221063841660525</v>
+        <v>1.172896763817737</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.65144019332481</v>
+        <v>4.622539946619137</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.259429139825408</v>
+        <v>-4.307596217668197</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.180464993932474</v>
+        <v>2.161198162795359</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.292785288674375</v>
+        <v>1.244618210831587</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.660264247381011</v>
+        <v>4.631364000675338</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.237056114217702</v>
+        <v>-4.28522319206049</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.136329950096728</v>
+        <v>2.117063118959613</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.304041039787277</v>
+        <v>1.255873961944489</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.613933443969923</v>
+        <v>4.58503319726425</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.270072410128447</v>
+        <v>-4.318239487971235</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.308321636617785</v>
+        <v>2.28905480548067</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.234603663120525</v>
+        <v>1.186436585277737</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.757469222855227</v>
+        <v>4.728568976149554</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.258544774478838</v>
+        <v>-4.306711852321627</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.304853916705878</v>
+        <v>2.285587085568763</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.293604321321888</v>
+        <v>1.2454372434791</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.784790843604294</v>
+        <v>4.755890596898621</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.355886275821207</v>
+        <v>-4.404053353663995</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.269585428690719</v>
+        <v>2.250318597553604</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.249184139156399</v>
+        <v>1.201017061313611</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.761806846826789</v>
+        <v>4.732906600121117</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.441742305161173</v>
+        <v>-4.489909383003962</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.236494099147571</v>
+        <v>2.217227268010455</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.206808069930264</v>
+        <v>1.158640992087476</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.737632287483946</v>
+        <v>4.708732040778274</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.450579102577293</v>
+        <v>-4.498746180420081</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.215378582001625</v>
+        <v>2.196111750864509</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.199365897288914</v>
+        <v>1.151198819446126</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.715586185719638</v>
+        <v>4.686685939013965</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.541961665142751</v>
+        <v>-4.59012874298554</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.188990068020491</v>
+        <v>2.169723236883375</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.162801012569569</v>
+        <v>1.114633934726781</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.70381176593308</v>
+        <v>4.674911519227408</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.530254947155745</v>
+        <v>-4.578422024998534</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.295801013039561</v>
+        <v>2.276534181902445</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.174507730556575</v>
+        <v>1.126340652713787</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.812964054549552</v>
+        <v>4.784063807843879</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.430591443072083</v>
+        <v>-4.478758520914871</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.33869875340443</v>
+        <v>2.319431922267315</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.237694813760262</v>
+        <v>1.189527735917474</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.853908643203169</v>
+        <v>4.825008396497496</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.440907541238435</v>
+        <v>-4.489074619081223</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.547477147415948</v>
+        <v>2.528210316278832</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.237694813760262</v>
+        <v>1.189527735917474</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.066813476481227</v>
+        <v>5.037913229775554</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.440813573221062</v>
+        <v>-4.488980651063851</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.546693401534986</v>
+        <v>2.527426570397871</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.066214060201707</v>
+        <v>5.037313813496034</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.448032397420906</v>
+        <v>-4.496199475263695</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.538037857799402</v>
+        <v>2.518771026662287</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.060446046146061</v>
+        <v>5.031545799440388</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.447083974302868</v>
+        <v>-4.495251052145656</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.538417227046618</v>
+        <v>2.519150395909502</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.060446046146061</v>
+        <v>5.031545799440388</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.604152432558491</v>
+        <v>-4.65231951040128</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.48831745172546</v>
+        <v>2.469050620588345</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.073173654127153</v>
+        <v>5.04427340742148</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.59816018576968</v>
+        <v>-4.646327263612468</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.492660348865373</v>
+        <v>2.473393517728257</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.075119652551541</v>
+        <v>5.046219405845868</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.509602224638912</v>
+        <v>-4.557769302481701</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.521737669335448</v>
+        <v>2.502470838198334</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.06877378856931</v>
+        <v>5.039873541863637</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.491843147135838</v>
+        <v>-4.540010224978626</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.528149977775674</v>
+        <v>2.508883146638559</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.23806467510758</v>
+        <v>1.189897597264792</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.068082466008305</v>
+        <v>5.039182219302632</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.39221299608677</v>
+        <v>-4.440380073929559</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.580784224103888</v>
+        <v>2.561517392966773</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.337694826156647</v>
+        <v>1.289527748313859</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.140642742546333</v>
+        <v>5.11174249584066</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.441612504775781</v>
+        <v>-4.48977958261857</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.750178686127009</v>
+        <v>2.730911854989895</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.347953659588392</v>
+        <v>1.299786581745604</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.335952308104106</v>
+        <v>5.307052061398433</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.234928031133405</v>
+        <v>-4.283095108976194</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.820041148686822</v>
+        <v>2.800774317549707</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.554638133230768</v>
+        <v>1.50647105538798</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.447151665392393</v>
+        <v>5.418251418686721</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.269084926130931</v>
+        <v>-4.31725200397372</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.808379904341916</v>
+        <v>2.789113073204802</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.471054363689956</v>
+        <v>1.422887285847168</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.399002917322011</v>
+        <v>5.370102670616338</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.176495447069475</v>
+        <v>-4.224662524912263</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.198912809956167</v>
+        <v>3.179645978819051</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.471054363689956</v>
+        <v>1.422887285847168</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.752500031311678</v>
+        <v>5.723599784606005</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.236384074893025</v>
+        <v>-4.284551152735814</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.17952047039385</v>
+        <v>3.160253639256735</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.456932449002491</v>
+        <v>1.408765371159703</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.748589994066303</v>
+        <v>5.71968974736063</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.184167765096683</v>
+        <v>-4.232334842939472</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.250236935635914</v>
+        <v>3.230970104498799</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.456932449002491</v>
+        <v>1.408765371159703</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.79841993538983</v>
+        <v>5.769519688684158</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.152270248011438</v>
+        <v>-4.200437325854226</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.271809912680023</v>
+        <v>3.252543081542908</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.488829966087737</v>
+        <v>1.440662888244949</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.826372415850988</v>
+        <v>5.797472169145315</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.861013924889161</v>
+        <v>3.79970519934194</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.169482872159705</v>
+        <v>-4.17305624435105</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.260562447059913</v>
+        <v>3.259133098183375</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.488829966087737</v>
+        <v>1.440662888244949</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.822009999890185</v>
+        <v>5.793109753184512</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.5%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-578.9%</t>
+          <t>-583.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-52.0%</t>
         </is>
       </c>
     </row>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,16 +49707,16 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.79970519934194</v>
+        <v>3.799705199341937</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.17305624435105</v>
+        <v>-4.215192650054367</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.259133098183375</v>
+        <v>3.242278535902049</v>
       </c>
       <c r="F2094" t="n">
         <v>1.440662888244949</v>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.799705199341937</v>
+        <v>3.79970519934194</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>181.2%</t>
+          <t>184.1%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>80.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>120.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>133.3%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2094"/>
+  <dimension ref="A1:G2095"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -49017,7 +49017,7 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736822870113276</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
@@ -49063,7 +49063,7 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
@@ -49109,7 +49109,7 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863552</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
@@ -49132,7 +49132,7 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394112</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
@@ -49155,7 +49155,7 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456729</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
@@ -49178,7 +49178,7 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883675</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
@@ -49201,7 +49201,7 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236296</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
@@ -49224,7 +49224,7 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427682</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.69183549961038</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
@@ -49293,7 +49293,7 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889189</v>
+        <v>3.673978374889188</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
@@ -49316,7 +49316,7 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409565</v>
+        <v>3.682476099409564</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
@@ -49339,7 +49339,7 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452571</v>
+        <v>3.67289517745257</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
@@ -49362,7 +49362,7 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762285</v>
+        <v>3.623960959762284</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
@@ -49385,7 +49385,7 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988016</v>
+        <v>3.633213467988015</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
@@ -49408,7 +49408,7 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
@@ -49431,7 +49431,7 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
@@ -49454,7 +49454,7 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
@@ -49477,7 +49477,7 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
@@ -49523,7 +49523,7 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720997</v>
+        <v>3.778232147720995</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
@@ -49546,7 +49546,7 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455271</v>
+        <v>3.775357097455269</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
@@ -49569,7 +49569,7 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.749078058963132</v>
+        <v>3.74907805896313</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
@@ -49592,7 +49592,7 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.740284389162542</v>
+        <v>3.74028438916254</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
@@ -49615,7 +49615,7 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.782482115652382</v>
+        <v>3.78248211565238</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
@@ -49638,7 +49638,7 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108671</v>
+        <v>3.809055905108669</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
@@ -49661,7 +49661,7 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.835202441103561</v>
+        <v>3.83520244110356</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
@@ -49684,7 +49684,7 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047744</v>
+        <v>3.821827147047742</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
@@ -49707,7 +49707,7 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.79970519934194</v>
+        <v>3.825268416650751</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
@@ -49723,6 +49723,29 @@
       </c>
       <c r="G2094" t="n">
         <v>5.793109753184512</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="2" t="n">
+        <v>45557</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>3.799792867574593</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>4.957255171852136</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>-4.215192650054367</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>3.242278535902049</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>1.440662888244949</v>
+      </c>
+      <c r="G2095" t="n">
+        <v>4.950318968838504</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539892</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811006</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382917</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013424</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800098</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74557314866085</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395087</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791149</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285647</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399468</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.69940464225637</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687012</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790802</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704757949437328</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736804952298395</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -48557,7 +48557,7 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539892</v>
       </c>
       <c r="C2044" t="n">
         <v>3.569941540005846</v>
@@ -48580,7 +48580,7 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811006</v>
       </c>
       <c r="C2045" t="n">
         <v>3.571822170189982</v>
@@ -48603,7 +48603,7 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382917</v>
       </c>
       <c r="C2046" t="n">
         <v>3.584673196067865</v>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.645256780013424</v>
       </c>
       <c r="C2047" t="n">
         <v>3.604875866241459</v>
@@ -48649,7 +48649,7 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
@@ -48672,7 +48672,7 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800098</v>
       </c>
       <c r="C2049" t="n">
         <v>3.548734015901807</v>
@@ -48695,7 +48695,7 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.74557314866085</v>
       </c>
       <c r="C2050" t="n">
         <v>3.555756634898747</v>
@@ -48718,7 +48718,7 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395087</v>
       </c>
       <c r="C2051" t="n">
         <v>3.654927634471652</v>
@@ -48741,7 +48741,7 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791149</v>
       </c>
       <c r="C2052" t="n">
         <v>3.842393859379944</v>
@@ -48764,7 +48764,7 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.811796810734027</v>
@@ -48787,7 +48787,7 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285647</v>
       </c>
       <c r="C2054" t="n">
         <v>3.815473213395745</v>
@@ -48810,7 +48810,7 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399468</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.81309126851924</v>
@@ -48833,7 +48833,7 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
         <v>3.810384507676875</v>
@@ -48856,7 +48856,7 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.689942600701</v>
       </c>
       <c r="C2057" t="n">
         <v>3.811813309820109</v>
@@ -48879,7 +48879,7 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711852429687012</v>
       </c>
       <c r="C2058" t="n">
         <v>3.911744549077862</v>
@@ -48902,7 +48902,7 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714879051790802</v>
       </c>
       <c r="C2059" t="n">
         <v>3.909530246203802</v>
@@ -48925,7 +48925,7 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437328</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
         <v>3.909433374278091</v>
@@ -48948,7 +48948,7 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298395</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
         <v>3.909427267836134</v>
@@ -49733,7 +49733,7 @@
         <v>3.799792867574593</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.957255171852136</v>
+        <v>4.957255171852137</v>
       </c>
       <c r="D2095" t="n">
         <v>-4.215192650054367</v>
@@ -49745,7 +49745,7 @@
         <v>1.440662888244949</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.950318968838504</v>
+        <v>4.950318968838505</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.1%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>184.1%</t>
+          <t>180.3%</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-37.6%</t>
+          <t>-38.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.5%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.7%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.1%</t>
+          <t>-583.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-52.0%</t>
+          <t>-53.2%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.1%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.2%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.7%</t>
+          <t>-320.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-80.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>80.5%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>119.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>132.0%</t>
         </is>
       </c>
     </row>
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.968777267064089</v>
+        <v>-3.982175240473294</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.983954839050599</v>
+        <v>1.978595649686917</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.124304474923259</v>
+        <v>1.110906501514055</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.246404855143938</v>
+        <v>4.238366071098415</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.900728704372559</v>
+        <v>-3.914126677781764</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.024025290005093</v>
+        <v>2.018666100641411</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.192353037614789</v>
+        <v>1.178955064205585</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.300085018636739</v>
+        <v>4.292046234591216</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.13232909754206</v>
+        <v>-4.145727070951264</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.951587802910887</v>
+        <v>1.946228613547205</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.192353037614789</v>
+        <v>1.178955064205585</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.320287688810333</v>
+        <v>4.31224890476481</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.18238064307128</v>
+        <v>-4.195778616480483</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.915173420766081</v>
+        <v>1.9098142314024</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.192353037614789</v>
+        <v>1.178955064205585</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.303893924877214</v>
+        <v>4.295855140831692</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.357487475647725</v>
+        <v>-4.370885449056928</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.80538260132897</v>
+        <v>1.800023411965288</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.192353037614789</v>
+        <v>1.178955064205585</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.264145838470681</v>
+        <v>4.256107054425159</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.161387322217202</v>
+        <v>-4.174785295626405</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.890845281698119</v>
+        <v>1.885486092334437</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.388453191045312</v>
+        <v>1.375055217636107</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.388828549525935</v>
+        <v>4.380789765480412</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.008361930103918</v>
+        <v>-4.021759903513121</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.051226438116337</v>
+        <v>2.045867248752656</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.541478583158596</v>
+        <v>1.528080609749392</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.57981478436681</v>
+        <v>4.571776000321287</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.036669243977189</v>
+        <v>-4.050067217386391</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.227369737475321</v>
+        <v>2.22201054811164</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.541478583158596</v>
+        <v>1.528080609749392</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.767281009275102</v>
+        <v>4.759242225229579</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.203262469090711</v>
+        <v>-4.216660442499913</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.130135398783995</v>
+        <v>2.124776209420314</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.374885358045073</v>
+        <v>1.361487384635869</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.636728025561071</v>
+        <v>4.628689241515549</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.180226675729145</v>
+        <v>-4.193624649138347</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.143026118790339</v>
+        <v>2.137666929426658</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.374885358045073</v>
+        <v>1.361487384635869</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.640404428222789</v>
+        <v>4.632365644177266</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.150980695273448</v>
+        <v>-4.164378668682651</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.152342566096113</v>
+        <v>2.146983376732432</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.374885358045073</v>
+        <v>1.361487384635869</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.638022483346284</v>
+        <v>4.629983699300761</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.257906243151299</v>
+        <v>-4.271304216560502</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.106865586102608</v>
+        <v>2.101506396738927</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.267959810167222</v>
+        <v>1.254561836758018</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.571160393777209</v>
+        <v>4.563121609731686</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.402924801658548</v>
+        <v>-4.416322775067751</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.050286964842943</v>
+        <v>2.044927775479261</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.122941251659973</v>
+        <v>1.109543278250769</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.485578060816094</v>
+        <v>4.477539276770571</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.521266567443265</v>
+        <v>-4.534664540852468</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.102881497786809</v>
+        <v>2.097522308423127</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.133627290222864</v>
+        <v>1.120229316813659</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.591920923211581</v>
+        <v>4.583882139166058</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.572676989763973</v>
+        <v>-4.586074963173176</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.080103025984465</v>
+        <v>2.074743836620783</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.133627290222864</v>
+        <v>1.120229316813659</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.58970662033752</v>
+        <v>4.581667836291998</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.652096440971725</v>
+        <v>-4.665494414380928</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.048238373575653</v>
+        <v>2.042879184211972</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.133627290222864</v>
+        <v>1.120229316813659</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.589609748411809</v>
+        <v>4.581570964366287</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.747559438888943</v>
+        <v>-4.760957412298145</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.010047067966809</v>
+        <v>2.004687878603128</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.133627290222864</v>
+        <v>1.120229316813659</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.589603641969852</v>
+        <v>4.58156485792433</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.683183528038228</v>
+        <v>-4.69658150144743</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.033893828869705</v>
+        <v>2.028534639506024</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.198003201073579</v>
+        <v>1.184605227664375</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.626325585042892</v>
+        <v>4.618286800997369</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.738552690170422</v>
+        <v>-4.751950663579624</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.017479981764555</v>
+        <v>2.012120792400873</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.198003201073579</v>
+        <v>1.184605227664375</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.632059402790619</v>
+        <v>4.624020618745096</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113276</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.75677115716803</v>
+        <v>-4.770169130577233</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.009730958308444</v>
+        <v>2.004371768944762</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.172896763817737</v>
+        <v>1.159498790408533</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.616533903780046</v>
+        <v>4.608495119734523</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.668564323020452</v>
+        <v>-4.681962296429655</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.064888084817794</v>
+        <v>2.059528895454112</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.172896763817737</v>
+        <v>1.159498790408533</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.636408296630364</v>
+        <v>4.628369512584841</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.562529327815143</v>
+        <v>-4.575927301224345</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.091002783424645</v>
+        <v>2.085643594060964</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.172896763817737</v>
+        <v>1.159498790408533</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.620108997155092</v>
+        <v>4.61207021310957</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.379317664682048</v>
+        <v>-4.39271563809125</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.166718398141929</v>
+        <v>2.161359208778247</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.172896763817737</v>
+        <v>1.159498790408533</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.622539946619137</v>
+        <v>4.614501162573616</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863552</v>
       </c>
       <c r="C2068" t="n">
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.307596217668197</v>
+        <v>-4.320994191077399</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.161198162795359</v>
+        <v>2.155838973431678</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.244618210831587</v>
+        <v>1.231220237422383</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.631364000675338</v>
+        <v>4.623325216629816</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.28522319206049</v>
+        <v>-4.298621165469693</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.117063118959613</v>
+        <v>2.111703929595932</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.255873961944489</v>
+        <v>1.242475988535285</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.58503319726425</v>
+        <v>4.576994413218728</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715607446456729</v>
       </c>
       <c r="C2070" t="n">
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.318239487971235</v>
+        <v>-4.331637461380438</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.28905480548067</v>
+        <v>2.283695616116989</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.186436585277737</v>
+        <v>1.173038611868533</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.728568976149554</v>
+        <v>4.720530192104032</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713762536883675</v>
       </c>
       <c r="C2071" t="n">
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.306711852321627</v>
+        <v>-4.320109825730829</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.285587085568763</v>
+        <v>2.280227896205082</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.2454372434791</v>
+        <v>1.232039270069895</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.755890596898621</v>
+        <v>4.747851812853098</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717150699236296</v>
       </c>
       <c r="C2072" t="n">
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.404053353663995</v>
+        <v>-4.417451327073198</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.250318597553604</v>
+        <v>2.244959408189922</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.201017061313611</v>
+        <v>1.187619087904407</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.732906600121117</v>
+        <v>4.724867816075594</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705201079427682</v>
       </c>
       <c r="C2073" t="n">
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.489909383003962</v>
+        <v>-4.503307356413164</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.217227268010455</v>
+        <v>2.211868078646774</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.158640992087476</v>
+        <v>1.145243018678272</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.708732040778274</v>
+        <v>4.700693256732752</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.498746180420081</v>
+        <v>-4.512144153829284</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.196111750864509</v>
+        <v>2.190752561500828</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.151198819446126</v>
+        <v>1.137800846036921</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.686685939013965</v>
+        <v>4.678647154968442</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.59012874298554</v>
+        <v>-4.603526716394742</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.169723236883375</v>
+        <v>2.164364047519694</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.114633934726781</v>
+        <v>1.101235961317577</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.674911519227408</v>
+        <v>4.666872735181885</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889188</v>
+        <v>3.673978374889189</v>
       </c>
       <c r="C2076" t="n">
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.578422024998534</v>
+        <v>-4.591819998407736</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.276534181902445</v>
+        <v>2.271174992538764</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.126340652713787</v>
+        <v>1.112942679304583</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.784063807843879</v>
+        <v>4.776025023798357</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409564</v>
+        <v>3.682476099409565</v>
       </c>
       <c r="C2077" t="n">
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.478758520914871</v>
+        <v>-4.492156494324074</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.319431922267315</v>
+        <v>2.314072732903634</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.189527735917474</v>
+        <v>1.17612976250827</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.825008396497496</v>
+        <v>4.816969612451973</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.67289517745257</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.489074619081223</v>
+        <v>-4.502472592490426</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.528210316278832</v>
+        <v>2.522851126915151</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.189527735917474</v>
+        <v>1.17612976250827</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.037913229775554</v>
+        <v>5.029874445730031</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762284</v>
+        <v>3.623960959762285</v>
       </c>
       <c r="C2079" t="n">
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.488980651063851</v>
+        <v>-4.502378624473053</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.527426570397871</v>
+        <v>2.52206738103419</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.037313813496034</v>
+        <v>5.029275029450512</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988015</v>
+        <v>3.633213467988016</v>
       </c>
       <c r="C2080" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.496199475263695</v>
+        <v>-4.509597448672897</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.518771026662287</v>
+        <v>2.513411837298606</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.031545799440388</v>
+        <v>5.023507015394865</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.495251052145656</v>
+        <v>-4.508649025554859</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.519150395909502</v>
+        <v>2.513791206545821</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.031545799440388</v>
+        <v>5.023507015394865</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.65231951040128</v>
+        <v>-4.665717483810482</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.469050620588345</v>
+        <v>2.463691431224664</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.04427340742148</v>
+        <v>5.036234623375957</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.646327263612468</v>
+        <v>-4.659725237021671</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.473393517728257</v>
+        <v>2.468034328364576</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.046219405845868</v>
+        <v>5.038180621800345</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.557769302481701</v>
+        <v>-4.571167275890903</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.502470838198334</v>
+        <v>2.497111648834652</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.039873541863637</v>
+        <v>5.031834757818114</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.540010224978626</v>
+        <v>-4.553408198387829</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.508883146638559</v>
+        <v>2.503523957274878</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.189897597264792</v>
+        <v>1.176499623855588</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.039182219302632</v>
+        <v>5.03114343525711</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.778232147720995</v>
+        <v>3.778232147720997</v>
       </c>
       <c r="C2086" t="n">
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.440380073929559</v>
+        <v>-4.453778047338761</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.561517392966773</v>
+        <v>2.556158203603092</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.289527748313859</v>
+        <v>1.276129774904655</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.11174249584066</v>
+        <v>5.103703711795137</v>
       </c>
     </row>
     <row r="2087">
@@ -49546,22 +49546,22 @@
         <v>45549</v>
       </c>
       <c r="B2087" t="n">
-        <v>3.775357097455269</v>
+        <v>3.775357097455271</v>
       </c>
       <c r="C2087" t="n">
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.48977958261857</v>
+        <v>-4.503177556027772</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.730911854989895</v>
+        <v>2.725552665626213</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.299786581745604</v>
+        <v>1.2863886083364</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.307052061398433</v>
+        <v>5.299013277352911</v>
       </c>
     </row>
     <row r="2088">
@@ -49569,22 +49569,22 @@
         <v>45550</v>
       </c>
       <c r="B2088" t="n">
-        <v>3.74907805896313</v>
+        <v>3.749078058963132</v>
       </c>
       <c r="C2088" t="n">
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.283095108976194</v>
+        <v>-4.296493082385396</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.800774317549707</v>
+        <v>2.795415128186026</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.50647105538798</v>
+        <v>1.493073081978776</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.418251418686721</v>
+        <v>5.410212634641198</v>
       </c>
     </row>
     <row r="2089">
@@ -49592,22 +49592,22 @@
         <v>45551</v>
       </c>
       <c r="B2089" t="n">
-        <v>3.74028438916254</v>
+        <v>3.740284389162542</v>
       </c>
       <c r="C2089" t="n">
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.31725200397372</v>
+        <v>-4.330649977382922</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.789113073204802</v>
+        <v>2.78375388384112</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.422887285847168</v>
+        <v>1.409489312437963</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.370102670616338</v>
+        <v>5.362063886570816</v>
       </c>
     </row>
     <row r="2090">
@@ -49615,22 +49615,22 @@
         <v>45552</v>
       </c>
       <c r="B2090" t="n">
-        <v>3.78248211565238</v>
+        <v>3.782482115652382</v>
       </c>
       <c r="C2090" t="n">
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.224662524912263</v>
+        <v>-4.238060498321466</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.179645978819051</v>
+        <v>3.17428678945537</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.422887285847168</v>
+        <v>1.409489312437963</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.723599784606005</v>
+        <v>5.715561000560482</v>
       </c>
     </row>
     <row r="2091">
@@ -49638,22 +49638,22 @@
         <v>45553</v>
       </c>
       <c r="B2091" t="n">
-        <v>3.809055905108669</v>
+        <v>3.809055905108671</v>
       </c>
       <c r="C2091" t="n">
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.284551152735814</v>
+        <v>-4.297949126145016</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.160253639256735</v>
+        <v>3.154894449893053</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.408765371159703</v>
+        <v>1.395367397750499</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.71968974736063</v>
+        <v>5.711650963315107</v>
       </c>
     </row>
     <row r="2092">
@@ -49661,22 +49661,22 @@
         <v>45554</v>
       </c>
       <c r="B2092" t="n">
-        <v>3.83520244110356</v>
+        <v>3.835202441103561</v>
       </c>
       <c r="C2092" t="n">
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.232334842939472</v>
+        <v>-4.245732816348674</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.230970104498799</v>
+        <v>3.225610915135118</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.408765371159703</v>
+        <v>1.395367397750499</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.769519688684158</v>
+        <v>5.761480904638635</v>
       </c>
     </row>
     <row r="2093">
@@ -49684,22 +49684,22 @@
         <v>45555</v>
       </c>
       <c r="B2093" t="n">
-        <v>3.821827147047742</v>
+        <v>3.821827147047744</v>
       </c>
       <c r="C2093" t="n">
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.200437325854226</v>
+        <v>-4.213835299263429</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.252543081542908</v>
+        <v>3.247183892179227</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.440662888244949</v>
+        <v>1.427264914835744</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.797472169145315</v>
+        <v>5.789433385099793</v>
       </c>
     </row>
     <row r="2094">
@@ -49707,22 +49707,22 @@
         <v>45556</v>
       </c>
       <c r="B2094" t="n">
-        <v>3.825268416650751</v>
+        <v>3.825268416650752</v>
       </c>
       <c r="C2094" t="n">
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.215192650054367</v>
+        <v>-4.228590623463569</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.242278535902049</v>
+        <v>3.236919346538367</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.440662888244949</v>
+        <v>1.427264914835744</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.793109753184512</v>
+        <v>5.78507096913899</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.799792867574593</v>
+        <v>3.782005177022191</v>
       </c>
       <c r="C2095" t="n">
-        <v>4.957255171852137</v>
+        <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.215192650054367</v>
+        <v>-4.221507014316025</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.242278535902049</v>
+        <v>3.230677293613665</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.440662888244949</v>
+        <v>1.434348523983289</v>
       </c>
       <c r="G2095" t="n">
-        <v>4.950318968838505</v>
+        <v>5.780245638043797</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240922.xlsx
+++ b/tame_output/ON/bt/strategyON_20240922.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-38.4%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-70.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>422.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.7%</t>
+          <t>-579.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-53.2%</t>
+          <t>-51.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-26.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>113.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.8%</t>
+          <t>-320.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-80.6%</t>
+          <t>-70.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>131.2%</t>
+          <t>133.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>119.8%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>132.0%</t>
+          <t>137.9%</t>
         </is>
       </c>
     </row>
@@ -48563,16 +48563,16 @@
         <v>3.569941540005846</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.927622147495868</v>
+        <v>-3.87945506965308</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.998536256693751</v>
+        <v>2.017803087830866</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.16545959449148</v>
+        <v>1.213626672334268</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.269217296700734</v>
+        <v>4.298117543406407</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.571822170189982</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.982175240473294</v>
+        <v>-3.920610189221301</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.978595649686917</v>
+        <v>2.003221670187714</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.110906501514055</v>
+        <v>1.172471552766047</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.238366071098415</v>
+        <v>4.275305101849611</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.584673196067865</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.914126677781764</v>
+        <v>-3.852561626529771</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.018666100641411</v>
+        <v>2.043292121142208</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.178955064205585</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.292046234591216</v>
+        <v>4.328985265342411</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.604875866241459</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.145727070951264</v>
+        <v>-4.084162019699273</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.946228613547205</v>
+        <v>1.970854634048002</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.178955064205585</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.31224890476481</v>
+        <v>4.349187935516005</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.588482102308341</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.195778616480483</v>
+        <v>-4.134213565228492</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.9098142314024</v>
+        <v>1.934440251903196</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.178955064205585</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.295855140831692</v>
+        <v>4.332794171582887</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.548734015901807</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.370885449056928</v>
+        <v>-4.309320397804937</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.800023411965288</v>
+        <v>1.824649432466085</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.178955064205585</v>
+        <v>1.240520115457577</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.256107054425159</v>
+        <v>4.293046085176353</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.555756634898747</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.174785295626405</v>
+        <v>-4.113220244374414</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.885486092334437</v>
+        <v>1.910112112835234</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.375055217636107</v>
+        <v>1.4366202688881</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.380789765480412</v>
+        <v>4.417728796231607</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.654927634471652</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.021759903513121</v>
+        <v>-3.96019485226113</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.045867248752656</v>
+        <v>2.070493269253452</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.528080609749392</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.571776000321287</v>
+        <v>4.608715031072482</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>3.842393859379944</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.050067217386391</v>
+        <v>-3.9885021661344</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.22201054811164</v>
+        <v>2.246636568612437</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.528080609749392</v>
+        <v>1.589645661001384</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.759242225229579</v>
+        <v>4.796181255980775</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.811796810734027</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.216660442499913</v>
+        <v>-4.155095391247922</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.124776209420314</v>
+        <v>2.14940222992111</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.361487384635869</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.628689241515549</v>
+        <v>4.665628272266744</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.815473213395745</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.193624649138347</v>
+        <v>-4.132059597886356</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.137666929426658</v>
+        <v>2.162292949927454</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.361487384635869</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.632365644177266</v>
+        <v>4.669304674928462</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.81309126851924</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.164378668682651</v>
+        <v>-4.10281361743066</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.146983376732432</v>
+        <v>2.171609397233228</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.361487384635869</v>
+        <v>1.423052435887861</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.629983699300761</v>
+        <v>4.666922730051957</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.810384507676875</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.271304216560502</v>
+        <v>-4.209739165308511</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.101506396738927</v>
+        <v>2.126132417239723</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.254561836758018</v>
+        <v>1.31612688801001</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.563121609731686</v>
+        <v>4.600060640482882</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.811813309820109</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.416322775067751</v>
+        <v>-4.35475772381576</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.044927775479261</v>
+        <v>2.069553795980058</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.109543278250769</v>
+        <v>1.171108329502762</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.477539276770571</v>
+        <v>4.514478307521767</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>3.911744549077862</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.534664540852468</v>
+        <v>-4.473099489600477</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.097522308423127</v>
+        <v>2.122148328923924</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.120229316813659</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.583882139166058</v>
+        <v>4.620821169917254</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>3.909530246203802</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.586074963173176</v>
+        <v>-4.524509911921185</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.074743836620783</v>
+        <v>2.099369857121579</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.120229316813659</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.581667836291998</v>
+        <v>4.618606867043193</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>3.909433374278091</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.665494414380928</v>
+        <v>-4.603929363128937</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.042879184211972</v>
+        <v>2.067505204712768</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.120229316813659</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.581570964366287</v>
+        <v>4.618509995117482</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>3.909427267836134</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.760957412298145</v>
+        <v>-4.699392361046154</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.004687878603128</v>
+        <v>2.029313899103924</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.120229316813659</v>
+        <v>1.181794368065652</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.58156485792433</v>
+        <v>4.618503888675525</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>3.907523664398744</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.69658150144743</v>
+        <v>-4.635016450195439</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.028534639506024</v>
+        <v>2.053160660006821</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.184605227664375</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.618286800997369</v>
+        <v>4.655225831748565</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>3.913257482146471</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.751950663579624</v>
+        <v>-4.690385612327633</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.012120792400873</v>
+        <v>2.036746812901669</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.184605227664375</v>
+        <v>1.246170278916367</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.624020618745096</v>
+        <v>4.660959649496291</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>3.912795845489403</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.770169130577233</v>
+        <v>-4.708604079325242</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.004371768944762</v>
+        <v>2.028997789445559</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.159498790408533</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.608495119734523</v>
+        <v>4.645434150485719</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>3.932670238339722</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.681962296429655</v>
+        <v>-4.680940832831336</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.059528895454112</v>
+        <v>2.059937480893439</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.159498790408533</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.628369512584841</v>
+        <v>4.665308543336037</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>3.91637093886445</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.575927301224345</v>
+        <v>-4.574905837626027</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.085643594060964</v>
+        <v>2.086052179500292</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.159498790408533</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.61207021310957</v>
+        <v>4.649009243860765</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>3.918801888328495</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.39271563809125</v>
+        <v>-4.391694174492931</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.161359208778247</v>
+        <v>2.161767794217575</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.159498790408533</v>
+        <v>1.221063841660525</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.614501162573616</v>
+        <v>4.65144019332481</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>3.884593074176385</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.320994191077399</v>
+        <v>-4.31997272747908</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.155838973431678</v>
+        <v>2.156247558871005</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.231220237422383</v>
+        <v>1.292785288674375</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.623325216629816</v>
+        <v>4.660264247381011</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>3.831508820097557</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.298621165469693</v>
+        <v>-4.297599701871374</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.111703929595932</v>
+        <v>2.112112515035259</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.242475988535285</v>
+        <v>1.304041039787277</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.576994413218728</v>
+        <v>4.613933443969923</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.016707024982912</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.331637461380438</v>
+        <v>-4.330615997782119</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.283695616116989</v>
+        <v>2.284104201556317</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.173038611868533</v>
+        <v>1.234603663120525</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.720530192104032</v>
+        <v>4.757469222855227</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.008628250811161</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.320109825730829</v>
+        <v>-4.31908836213251</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.280227896205082</v>
+        <v>2.280636481644409</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.232039270069895</v>
+        <v>1.293604321321888</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.747851812853098</v>
+        <v>4.784790843604294</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.01229636333295</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.417451327073198</v>
+        <v>-4.416429863474879</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.244959408189922</v>
+        <v>2.24536799362925</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.187619087904407</v>
+        <v>1.249184139156399</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.724867816075594</v>
+        <v>4.761806846826789</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.013547445525788</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.503307356413164</v>
+        <v>-4.502285892814846</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.211868078646774</v>
+        <v>2.212276664086102</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.145243018678272</v>
+        <v>1.206808069930264</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.700693256732752</v>
+        <v>4.737632287483946</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>3.99596664734629</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.512144153829284</v>
+        <v>-4.511122690230965</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.190752561500828</v>
+        <v>2.191161146940155</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.137800846036921</v>
+        <v>1.199365897288914</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.678647154968442</v>
+        <v>4.715586185719638</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.006131158391339</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.603526716394742</v>
+        <v>-4.602505252796424</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.164364047519694</v>
+        <v>2.164772632959021</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.101235961317577</v>
+        <v>1.162801012569569</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.666872735181885</v>
+        <v>4.70381176593308</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.108259416215606</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.591819998407736</v>
+        <v>-4.590798534809418</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.271174992538764</v>
+        <v>2.271583577978091</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.112942679304583</v>
+        <v>1.174507730556575</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.776025023798357</v>
+        <v>4.812964054549552</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.111291754947011</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.492156494324074</v>
+        <v>-4.491135030725755</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.314072732903634</v>
+        <v>2.314481318342961</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.17612976250827</v>
+        <v>1.237694813760262</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.816969612451973</v>
+        <v>4.853908643203169</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.324196588225069</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.502472592490426</v>
+        <v>-4.501451128892107</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.522851126915151</v>
+        <v>2.523259712354478</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.17612976250827</v>
+        <v>1.237694813760262</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.029874445730031</v>
+        <v>5.066813476481227</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.323375255137159</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.502378624473053</v>
+        <v>-4.501357160874734</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.52206738103419</v>
+        <v>2.522475966473517</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.029275029450512</v>
+        <v>5.066214060201707</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.509597448672897</v>
+        <v>-4.508575985074579</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.513411837298606</v>
+        <v>2.513820422737933</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.023507015394865</v>
+        <v>5.060446046146061</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.317607241081513</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.508649025554859</v>
+        <v>-4.50762756195654</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.513791206545821</v>
+        <v>2.514199791985149</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.023507015394865</v>
+        <v>5.060446046146061</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.330334849062605</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.665717483810482</v>
+        <v>-4.664696020212164</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.463691431224664</v>
+        <v>2.464100016663991</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.036234623375957</v>
+        <v>5.073173654127153</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.332280847486992</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.659725237021671</v>
+        <v>-4.658703773423352</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.468034328364576</v>
+        <v>2.468442913803904</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.038180621800345</v>
+        <v>5.075119652551541</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.325934983504761</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.571167275890903</v>
+        <v>-4.570145812292584</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.497111648834652</v>
+        <v>2.49752023427398</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.031834757818114</v>
+        <v>5.06877378856931</v>
       </c>
     </row>
     <row r="2085">
@@ -49506,16 +49506,16 @@
         <v>4.325243660943757</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.553408198387829</v>
+        <v>-4.55238673478951</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.503523957274878</v>
+        <v>2.503932542714205</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.176499623855588</v>
+        <v>1.23806467510758</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.03114343525711</v>
+        <v>5.068082466008305</v>
       </c>
     </row>
     <row r="2086">
@@ -49529,16 +49529,16 @@
         <v>4.338025846852344</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.453778047338761</v>
+        <v>-4.452756583740443</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.556158203603092</v>
+        <v>2.556566789042419</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.276129774904655</v>
+        <v>1.337694826156647</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.103703711795137</v>
+        <v>5.140642742546333</v>
       </c>
     </row>
     <row r="2087">
@@ -49552,16 +49552,16 @@
         <v>4.52718011235107</v>
       </c>
       <c r="D2087" t="n">
-        <v>-4.503177556027772</v>
+        <v>-4.502156092429454</v>
       </c>
       <c r="E2087" t="n">
-        <v>2.725552665626213</v>
+        <v>2.725961251065541</v>
       </c>
       <c r="F2087" t="n">
-        <v>1.2863886083364</v>
+        <v>1.347953659588392</v>
       </c>
       <c r="G2087" t="n">
-        <v>5.299013277352911</v>
+        <v>5.335952308104106</v>
       </c>
     </row>
     <row r="2088">
@@ -49575,16 +49575,16 @@
         <v>4.514368785453932</v>
       </c>
       <c r="D2088" t="n">
-        <v>-4.296493082385396</v>
+        <v>-4.295471618787078</v>
       </c>
       <c r="E2088" t="n">
-        <v>2.795415128186026</v>
+        <v>2.795823713625353</v>
       </c>
       <c r="F2088" t="n">
-        <v>1.493073081978776</v>
+        <v>1.554638133230768</v>
       </c>
       <c r="G2088" t="n">
-        <v>5.410212634641198</v>
+        <v>5.447151665392393</v>
       </c>
     </row>
     <row r="2089">
@@ -49598,16 +49598,16 @@
         <v>4.516370299108037</v>
       </c>
       <c r="D2089" t="n">
-        <v>-4.330649977382922</v>
+        <v>-4.329628513784604</v>
       </c>
       <c r="E2089" t="n">
-        <v>2.78375388384112</v>
+        <v>2.784162469280448</v>
       </c>
       <c r="F2089" t="n">
-        <v>1.409489312437963</v>
+        <v>1.471054363689956</v>
       </c>
       <c r="G2089" t="n">
-        <v>5.362063886570816</v>
+        <v>5.399002917322011</v>
       </c>
     </row>
     <row r="2090">
@@ -49621,16 +49621,16 @@
         <v>4.869867413097705</v>
       </c>
       <c r="D2090" t="n">
-        <v>-4.238060498321466</v>
+        <v>-4.237039034723147</v>
       </c>
       <c r="E2090" t="n">
-        <v>3.17428678945537</v>
+        <v>3.174695374894698</v>
       </c>
       <c r="F2090" t="n">
-        <v>1.409489312437963</v>
+        <v>1.471054363689956</v>
       </c>
       <c r="G2090" t="n">
-        <v>5.715561000560482</v>
+        <v>5.752500031311678</v>
       </c>
     </row>
     <row r="2091">
@@ -49644,16 +49644,16 @@
         <v>4.874430524664808</v>
       </c>
       <c r="D2091" t="n">
-        <v>-4.297949126145016</v>
+        <v>-4.296927662546698</v>
       </c>
       <c r="E2091" t="n">
-        <v>3.154894449893053</v>
+        <v>3.155303035332381</v>
       </c>
       <c r="F2091" t="n">
-        <v>1.395367397750499</v>
+        <v>1.456932449002491</v>
       </c>
       <c r="G2091" t="n">
-        <v>5.711650963315107</v>
+        <v>5.748589994066303</v>
       </c>
     </row>
     <row r="2092">
@@ -49667,16 +49667,16 @@
         <v>4.924260465988335</v>
       </c>
       <c r="D2092" t="n">
-        <v>-4.245732816348674</v>
+        <v>-4.244711352750356</v>
       </c>
       <c r="E2092" t="n">
-        <v>3.225610915135118</v>
+        <v>3.226019500574445</v>
       </c>
       <c r="F2092" t="n">
-        <v>1.395367397750499</v>
+        <v>1.456932449002491</v>
       </c>
       <c r="G2092" t="n">
-        <v>5.761480904638635</v>
+        <v>5.79841993538983</v>
       </c>
     </row>
     <row r="2093">
@@ -49690,16 +49690,16 @@
         <v>4.933074436198346</v>
       </c>
       <c r="D2093" t="n">
-        <v>-4.213835299263429</v>
+        <v>-4.21281383566511</v>
       </c>
       <c r="E2093" t="n">
-        <v>3.247183892179227</v>
+        <v>3.247592477618555</v>
       </c>
       <c r="F2093" t="n">
-        <v>1.427264914835744</v>
+        <v>1.488829966087737</v>
       </c>
       <c r="G2093" t="n">
-        <v>5.789433385099793</v>
+        <v>5.826372415850988</v>
       </c>
     </row>
     <row r="2094">
@@ -49713,16 +49713,16 @@
         <v>4.928712020237543</v>
       </c>
       <c r="D2094" t="n">
-        <v>-4.228590623463569</v>
+        <v>-4.227569159865251</v>
       </c>
       <c r="E2094" t="n">
-        <v>3.236919346538367</v>
+        <v>3.237327931977695</v>
       </c>
       <c r="F2094" t="n">
-        <v>1.427264914835744</v>
+        <v>1.488829966087737</v>
       </c>
       <c r="G2094" t="n">
-        <v>5.78507096913899</v>
+        <v>5.822009999890185</v>
       </c>
     </row>
     <row r="2095">
@@ -49730,22 +49730,22 @@
         <v>45557</v>
       </c>
       <c r="B2095" t="n">
-        <v>3.782005177022191</v>
+        <v>3.759791282939219</v>
       </c>
       <c r="C2095" t="n">
         <v>4.919636523653823</v>
       </c>
       <c r="D2095" t="n">
-        <v>-4.221507014316025</v>
+        <v>-4.183448949994706</v>
       </c>
       <c r="E2095" t="n">
-        <v>3.230677293613665</v>
+        <v>3.245900519342193</v>
       </c>
       <c r="F2095" t="n">
-        <v>1.434348523983289</v>
+        <v>1.532950175958281</v>
       </c>
       <c r="G2095" t="n">
-        <v>5.780245638043797</v>
+        <v>5.839406629228792</v>
       </c>
     </row>
   </sheetData>
